--- a/data_extactor/batch_10_fa/trimmed/batch_0009_fa_trim.xlsx
+++ b/data_extactor/batch_10_fa/trimmed/batch_0009_fa_trim.xlsx
@@ -508,12 +508,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>درک مطلب | شنیدن فعال | تفکر انتقادی | سخن گفتن | نگارش | نظارت | یادگیری فعال | راهبردهای یادگیری | ریاضیات</t>
+          <t>درک مطلب | گوش دادن فعال | تفکر انتقادی | سخن گفتن | نگارش | نظارت | یادگیری فعال | راهبردهای یادگیری | ریاضیات</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>مدیریت و امور اداری | خدمات مشتریان و خدمات فردی | ریاضیات | رایانه و الکترونیک | اقتصاد و حسابداری | امور کارکنان و منابع انسانی | حقوق و مقررات دولتی</t>
+          <t>مدیریت و اداره | خدمات مشتری و شخصی | ریاضیات | رایانه و الکترونیک | اقتصاد و حسابداری | پرسنل و منابع انسانی | قانون و دولت</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -528,7 +528,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>کارشناسان برنامه‌ریزی تداوم کسب‌وکار | کارشناسان تحلیل هوش تجاری | کارشناسان تحلیل سیستم‌های کامپیوتری | روان‌شناسان صنعتی و سازمانی | کارشناسان تحلیل تحقیقات بازار و بازاریابی | کارشناسان تحلیل تحقیق در عملیات | متخصصان مدیریت پروژه</t>
+          <t>کارشناسان برنامه‌ریزی تداوم کسب‌وکار | تحلیل‌گران هوش تجاری | تحلیل‌گران سیستم‌های کامپیوتری | روان‌شناسان صنعتی و سازمانی | کارشناسان تحلیل تحقیقات بازار و بازاریابی | تحلیل‌گران تحقیق در عملیات | کارشناسان مدیریت پروژه</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -565,17 +565,17 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>شنیدن فعال | درک مطلب | سخن گفتن | تفکر انتقادی | نگارش | نظارت | یادگیری فعال</t>
+          <t>گوش دادن فعال | درک مطلب | سخن گفتن | تفکر انتقادی | نگارش | نظارت | یادگیری فعال</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>خدمات مشتریان و خدمات فردی | زبان انگلیسی | ارتباطات و رسانه | امور اداری و دفتری | مدیریت و امور اداری | رایانه و الکترونیک | ایمنی و امنیت عمومی</t>
+          <t>خدمات مشتری و شخصی | زبان انگلیسی | ارتباطات و رسانه | اداری | مدیریت و اداره | رایانه و الکترونیک | ایمنی و امنیت عمومی</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>درک شفاهی | درک کتبی | بیان شفاهی | بیان کتبی | حساسیت به مسئله | استدلال قیاسی | مرتب‌سازی اطلاعات</t>
+          <t>درک شفاهی | درک کتبی | بیان شفاهی | بیان کتبی | حساسیت به مسئله | استدلال قیاسی | ترتیب‌دهی اطلاعات</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -585,7 +585,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>مدیران برنامه‌ها و کارگزاران هنرمندان، مجریان و ورزشکاران | مسئولان دفاتر و دستیاران اجرایی مدیریت | کارشناسان جذب منابع مالی و حامی | مدیران جذب منابع مالی | کارشناسان روابط عمومی | کارشناسان امور تفریحی و اوقات فراغت | مسئولان امور دفتری و کارشناسان امور اداری</t>
+          <t>مدیران برنامه‌ها و نمایندگان هنرمندان، مجریان و ورزشکاران | مسئولان دفاتر و دستیاران اجرایی مدیریت | کارشناسان جذب منابع مالی و حامی | مدیران جذب منابع مالی و حامیان | کارشناسان روابط عمومی | کارکنان و متصدیان امور تفریحی و اوقات فراغت | منشی‌ها و دستیاران اداری عمومی</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -622,17 +622,17 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>سخن گفتن | نگارش | شنیدن فعال | درک مطلب | تفکر انتقادی | یادگیری فعال | نظارت | ریاضیات</t>
+          <t>سخن گفتن | نگارش | گوش دادن فعال | درک مطلب | تفکر انتقادی | یادگیری فعال | نظارت | ریاضیات</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>خدمات مشتریان و خدمات فردی | فروش و بازاریابی | مدیریت و امور اداری | ارتباطات و رسانه | اقتصاد و حسابداری | رایانه و الکترونیک | امور اداری و دفتری</t>
+          <t>خدمات مشتری و شخصی | فروش و بازاریابی | مدیریت و اداره | ارتباطات و رسانه | اقتصاد و حسابداری | رایانه و الکترونیک | اداری</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>بیان شفاهی | درک شفاهی | درک کتبی | بیان کتبی | استدلال استقرایی | روانی کلام و ایده‌پردازی | حساسیت به مسئله</t>
+          <t>بیان شفاهی | درک شفاهی | درک کتبی | بیان کتبی | استدلال استقرایی | روانی ایده‌ها | حساسیت به مسئله</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -642,7 +642,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>مدیران تبلیغات و بازاریابی ترویجی | مدیران جذب منابع مالی | کارشناسان تحلیل تحقیقات بازار و بازاریابی | کارشناسان برنامه‌ریزی و برگزاری همایش‌ها و رویدادها | مدیران روابط عمومی | کارشناسان روابط عمومی | مدیران خدمات اجتماعی و عام‌المنفعه</t>
+          <t>مدیران تبلیغات و روابط ترویجی | مدیران جذب منابع مالی و حامیان | کارشناسان تحلیل تحقیقات بازار و بازاریابی | کارشناسان برنامه‌ریزی و برگزاری همایش‌ها و رویدادها | مدیران روابط عمومی | کارشناسان روابط عمومی | مدیران خدمات اجتماعی و خدمات مردمی</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -679,17 +679,17 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>درک مطلب | شنیدن فعال | سخن گفتن | تفکر انتقادی | نگارش | یادگیری فعال | ریاضیات | نظارت</t>
+          <t>درک مطلب | گوش دادن فعال | سخن گفتن | تفکر انتقادی | نگارش | یادگیری فعال | ریاضیات | نظارت</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>امور کارکنان و منابع انسانی | ریاضیات | مدیریت و امور اداری | اقتصاد و حسابداری | امور اداری و دفتری | حقوق و مقررات دولتی</t>
+          <t>پرسنل و منابع انسانی | ریاضیات | مدیریت و اداره | اقتصاد و حسابداری | اداری | قانون و دولت</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>بیان شفاهی | درک شفاهی | درک کتبی | حساسیت به مسئله | استدلال قیاسی | بیان کتبی | مرتب‌سازی اطلاعات</t>
+          <t>بیان شفاهی | درک شفاهی | درک کتبی | حساسیت به مسئله | استدلال قیاسی | بیان کتبی | ترتیب‌دهی اطلاعات</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -699,7 +699,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>کارشناسان تحلیل بودجه | مدیران حقوق و مزایا و جبران خدمت | دستیاران امور اداری و منابع انسانی، به‌جز حقوق و دستمزد و کارکرد | مدیران منابع انسانی | کارشناسان منابع انسانی | کارشناسان روابط کار و امور تشکل‌های کارگری | متصدیان امور کارکرد و حقوق و دستمزد</t>
+          <t>تحلیل‌گران بودجه | مدیران جبران خدمت و مزایا | دستیاران منابع انسانی، به جز حقوق و دستمزد و ثبت ساعات کار | مدیران منابع انسانی | کارشناسان منابع انسانی | کارشناسان روابط کار و امور تشکل‌های کارگری | کارمندان امور حقوق، دستمزد و ثبت زمان</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -736,17 +736,17 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>سخن گفتن | راهبردهای یادگیری | شنیدن فعال | درک مطلب | نگارش | تفکر انتقادی | یادگیری فعال | نظارت</t>
+          <t>سخن گفتن | راهبردهای یادگیری | گوش دادن فعال | درک مطلب | نگارش | تفکر انتقادی | یادگیری فعال | نظارت</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>آموزش و تدریس | خدمات مشتریان و خدمات فردی | زبان انگلیسی | امور کارکنان و منابع انسانی | مدیریت و امور اداری | روان‌شناسی | ارتباطات و رسانه</t>
+          <t>آموزش و پرورش | خدمات مشتری و شخصی | زبان انگلیسی | پرسنل و منابع انسانی | مدیریت و اداره | روان‌شناسی | ارتباطات و رسانه</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>بیان شفاهی | درک شفاهی | درک کتبی | بیان کتبی | روانی کلام و ایده‌پردازی | حساسیت به مسئله | استدلال قیاسی</t>
+          <t>بیان شفاهی | درک شفاهی | درک کتبی | بیان کتبی | روانی ایده‌ها | حساسیت به مسئله | استدلال قیاسی</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -756,7 +756,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>مدرسان آموزش‌های فنی، مهارتی و کاربردی، آموزش عالی | مشاوران و راهنمایان تحصیلی، شغلی و تربیتی | مدیران منابع انسانی | کارشناسان منابع انسانی | کارشناسان هماهنگی و برنامه‌ریزی درسی | مدیران آموزش و بهسازی منابع انسانی | مدرسان و معلمان خصوصی</t>
+          <t>مدرسان آموزش‌های فنی و حرفه‌ای در آموزش عالی | مشاوران تحصیلی، شغلی و هدایت استعدادها | مدیران منابع انسانی | کارشناسان منابع انسانی | کارشناسان و هماهنگ‌کنندگان برنامه‌ریزی درسی و آموزشی | مدیران آموزش و بهسازی | معلمان خصوصی و مدرسان تقویتی</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -793,17 +793,17 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>تفکر انتقادی | نگارش | درک مطلب | شنیدن فعال | سخن گفتن | یادگیری فعال | نظارت | ریاضیات | راهبردهای یادگیری</t>
+          <t>تفکر انتقادی | نگارش | درک مطلب | گوش دادن فعال | سخن گفتن | یادگیری فعال | نظارت | ریاضیات | راهبردهای یادگیری</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>خدمات مشتریان و خدمات فردی | فروش و بازاریابی | ریاضیات | مدیریت و امور اداری | ارتباطات و رسانه | رایانه و الکترونیک | اقتصاد و حسابداری</t>
+          <t>خدمات مشتری و شخصی | فروش و بازاریابی | ریاضیات | مدیریت و اداره | ارتباطات و رسانه | رایانه و الکترونیک | اقتصاد و حسابداری</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>استدلال استقرایی | درک کتبی | بیان شفاهی | بیان کتبی | استدلال قیاسی | درک شفاهی | مرتب‌سازی اطلاعات</t>
+          <t>استدلال استقرایی | درک کتبی | بیان شفاهی | بیان کتبی | استدلال قیاسی | درک شفاهی | ترتیب‌دهی اطلاعات</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -813,7 +813,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>کارشناسان تحلیل هوش تجاری | دانشمندان علم داده | کارشناسان تحلیل مدیریت و روش‌ها | مدیران بازاریابی | کارشناسان فروش اینترنتی و تجارت الکترونیک | کارشناسان تدوین راهبرد بازاریابی موتورهای جستجو | کارشناسان پژوهش‌های پیمایشی و نظرسنجی</t>
+          <t>تحلیل‌گران هوش تجاری | دانشمندان داده | کارشناسان تحلیل مدیریت و روش‌ها | مدیران بازاریابی | کارشناسان تجارت الکترونیک و فروشگاه‌های اینترنتی | کارشناسان تدوین راهبرد بازاریابی موتورهای جستجو | پژوهشگران پیمایشی و افکارسنجی</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -850,17 +850,17 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>درک مطلب | یادگیری فعال | شنیدن فعال | تفکر انتقادی | سخن گفتن | نگارش | نظارت</t>
+          <t>درک مطلب | یادگیری فعال | گوش دادن فعال | تفکر انتقادی | سخن گفتن | نگارش | نظارت</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>فروش و بازاریابی | رایانه و الکترونیک | زبان انگلیسی | ارتباطات و رسانه | ریاضیات | خدمات مشتریان و خدمات فردی</t>
+          <t>فروش و بازاریابی | رایانه و الکترونیک | زبان انگلیسی | ارتباطات و رسانه | ریاضیات | خدمات مشتری و شخصی</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>درک شفاهی | درک کتبی | بیان شفاهی | بیان کتبی | روانی کلام و ایده‌پردازی | حساسیت به مسئله | مرتب‌سازی اطلاعات</t>
+          <t>درک شفاهی | درک کتبی | بیان شفاهی | بیان کتبی | روانی ایده‌ها | حساسیت به مسئله | ترتیب‌دهی اطلاعات</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -870,7 +870,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>کارشناسان تحلیل هوش تجاری | کارشناسان تحلیل تحقیقات بازار و بازاریابی | مدیران بازاریابی | کارشناسان فروش اینترنتی و تجارت الکترونیک | مدیران و راهبران وب‌سایت | توسعه‌دهندگان وب | نویسندگان، مؤلفان و پدیدآورندگان محتوا</t>
+          <t>تحلیل‌گران هوش تجاری | کارشناسان تحلیل تحقیقات بازار و بازاریابی | مدیران بازاریابی | کارشناسان تجارت الکترونیک و فروشگاه‌های اینترنتی | مدیران وب | توسعه‌دهندگان وب | نویسندگان و پدیدآورندگان</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -907,17 +907,17 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>درک مطلب | تفکر انتقادی | شنیدن فعال | سخن گفتن | نگارش | نظارت | یادگیری فعال | راهبردهای یادگیری</t>
+          <t>درک مطلب | تفکر انتقادی | گوش دادن فعال | سخن گفتن | نگارش | نظارت | یادگیری فعال | راهبردهای یادگیری</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>مدیریت و امور اداری | خدمات مشتریان و خدمات فردی | اقتصاد و حسابداری | رایانه و الکترونیک | ریاضیات | امور کارکنان و منابع انسانی | حقوق و مقررات دولتی</t>
+          <t>مدیریت و اداره | خدمات مشتری و شخصی | اقتصاد و حسابداری | رایانه و الکترونیک | ریاضیات | پرسنل و منابع انسانی | قانون و دولت</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>درک شفاهی | درک کتبی | بیان شفاهی | بیان کتبی | استدلال قیاسی | مرتب‌سازی اطلاعات | حساسیت به مسئله</t>
+          <t>درک شفاهی | درک کتبی | بیان شفاهی | بیان کتبی | استدلال قیاسی | ترتیب‌دهی اطلاعات | حساسیت به مسئله</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -927,7 +927,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>کارشناسان تحلیل مدیریت و روش‌ها | متخصصان مدیریت پروژه | کارشناسان لجستیک و زنجیره تأمین | کارشناسان ارزیابی و انطباق قانونی | کارشناسان منابع انسانی | کارشناسان تحلیل تحقیقات بازار و بازاریابی | حسابداران و حسابرسان</t>
+          <t>کارشناسان تحلیل مدیریت و روش‌ها | کارشناسان مدیریت پروژه | کارشناسان لجستیک و مدیریت زنجیره تأمین | کارشناسان پایش انطباق و بازرسی مقرراتی | کارشناسان منابع انسانی | کارشناسان تحلیل تحقیقات بازار و بازاریابی | حسابداران و حسابرسان</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -964,17 +964,17 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>شنیدن فعال | تفکر انتقادی | درک مطلب | یادگیری فعال | سخن گفتن | نگارش | نظارت | راهبردهای یادگیری</t>
+          <t>گوش دادن فعال | تفکر انتقادی | درک مطلب | یادگیری فعال | سخن گفتن | نگارش | نظارت | راهبردهای یادگیری</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>ایمنی و امنیت عمومی | مدیریت و امور اداری | رایانه و الکترونیک | آموزش و تدریس | ارتباطات و رسانه | امور اداری و دفتری</t>
+          <t>ایمنی و امنیت عمومی | مدیریت و اداره | رایانه و الکترونیک | آموزش و پرورش | ارتباطات و رسانه | اداری</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>حساسیت به مسئله | استدلال استقرایی | درک شفاهی | درک کتبی | بیان کتبی | استدلال قیاسی | مرتب‌سازی اطلاعات</t>
+          <t>حساسیت به مسئله | استدلال استقرایی | درک شفاهی | درک کتبی | بیان کتبی | استدلال قیاسی | ترتیب‌دهی اطلاعات</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>مدیران انطباق و نظارت قانونی | مدیران فناوری اطلاعات و سیستم‌های کامپیوتری | مدیران مدیریت بحران | کارشناسان تحلیل امنیت اطلاعات | کارشناسان تحلیل مدیریت و روش‌ها | کارشناسان مدیریت امنیت | مدیران حراست و امنیت</t>
+          <t>مدیران تطبیق و نظارت مقرراتی | مدیران فناوری اطلاعات و سیستم‌های رایانه‌ای | مدیران مدیریت بحران و پدافند غیرعامل | تحلیل‌گران امنیت اطلاعات | کارشناسان تحلیل مدیریت و روش‌ها | کارشناسان مدیریت حراست و امنیت فیزیکی | مدیران حراست و انتظامات</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1021,12 +1021,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>سخن گفتن | نگارش | درک مطلب | شنیدن فعال | تفکر انتقادی | نظارت | یادگیری فعال | راهبردهای یادگیری</t>
+          <t>سخن گفتن | نگارش | درک مطلب | گوش دادن فعال | تفکر انتقادی | نظارت | یادگیری فعال | راهبردهای یادگیری</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>مدیریت و امور اداری | حقوق و مقررات دولتی | آموزش و تدریس | ساختمان و سازه | ارتباطات و رسانه | مهندسی و فناوری</t>
+          <t>مدیریت و اداره | قانون و دولت | آموزش و پرورش | ساختمان و ساخت‌وساز | ارتباطات و رسانه | مهندسی و فناوری</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -1041,7 +1041,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>کارشناسان تحلیل سیاست‌های تغییر اقلیم | دانشمندان حفاظت از منابع طبیعی | کارشناسان ممیزی انرژی | مهندسان محیط‌زیست | دانشمندان و متخصصان محیط‌زیست و سلامت | بوم‌شناسان و اکولوژیست‌های صنعتی | مهندسان شهرسازی و برنامه‌ریزی شهری و منطقه‌ای</t>
+          <t>تحلیل‌گران خط‌مشی تغییر اقلیم | دانشمندان حفاظت از منابع طبیعی | ممیزان انرژی | مهندسان محیط‌زیست | کارشناسان و متخصصان علوم محیطی (شامل بهداشت) | بوم‌شناسان صنعتی | برنامه‌ریزان شهری و منطقه‌ای</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
